--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260626.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>34,835</t>
+          <t>34,511</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.62%</t>
+          <t>10.51%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>84,203</t>
+          <t>83,418</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.93%</t>
+          <t>9.79%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>97,127</t>
+          <t>96,222</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.88%</t>
+          <t>8.52%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>38,232</t>
+          <t>37,876</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.72%</t>
+          <t>7.59%</t>
         </is>
       </c>
     </row>
@@ -699,56 +699,56 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>209,850</t>
+          <t>207,895</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>5.37%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>52,684</t>
+          <t>110,567</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>111,607</t>
+          <t>52,193</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>3.83%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>121,042</t>
+          <t>119,914</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20,838</t>
+          <t>20,644</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>63,398</t>
+          <t>62,808</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>125,899</t>
+          <t>124,726</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>58,310</t>
+          <t>57,767</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>146,564</t>
+          <t>145,198</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>24,228</t>
+          <t>24,002</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>26,133</t>
+          <t>25,890</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>66,994</t>
+          <t>66,370</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12,191</t>
+          <t>12,077</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>53,481</t>
+          <t>52,983</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1007,78 +1007,78 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>39,549</t>
+          <t>39,180</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>55,066</t>
+          <t>34,632</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>34,958</t>
+          <t>54,552</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>23,934</t>
+          <t>5,242</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1095,56 +1095,56 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>82,799</t>
+          <t>82,027</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>5,292</t>
+          <t>53,328</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>53,829</t>
+          <t>23,711</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1161,56 +1161,56 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>32,737</t>
+          <t>32,432</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>9,682</t>
+          <t>50,097</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>50,568</t>
+          <t>29,368</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1227,34 +1227,34 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>22,268</t>
+          <t>22,061</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>29,645</t>
+          <t>9,592</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,448</t>
+          <t>11,341</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,250</t>
+          <t>14,117</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>80,727</t>
+          <t>79,975</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>102,221</t>
+          <t>101,269</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>32,597</t>
+          <t>32,293</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>156,934</t>
+          <t>155,472</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1403,144 +1403,144 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>33,002</t>
+          <t>32,694</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,341</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14,300</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>14,434</t>
+          <t>27,464</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>6,320</t>
+          <t>46,322</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>27,722</t>
+          <t>6,261</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>46,758</t>
+          <t>7,273</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>3,926</t>
+          <t>3,889</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>17,342</t>
+          <t>17,180</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>101,617</t>
+          <t>100,670</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>25,290</t>
+          <t>25,054</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>3,053</t>
+          <t>3,024</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,625</t>
+          <t>8,545</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>19,842</t>
+          <t>19,657</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>41,142</t>
+          <t>40,758</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>124,017,790</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
